--- a/Modif_fichier_preset/test1.xlsx
+++ b/Modif_fichier_preset/test1.xlsx
@@ -1,77 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/44f8247593f74f89/Documents/RaC/Projet/pole  implémentation/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{F4F73971-42DB-44ED-9554-7149BAE2CB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0F66722-7487-4B1A-B896-2430CC98689B}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1932" yWindow="0" windowWidth="20928" windowHeight="12240" activeTab="1" xr2:uid="{8C062662-14E7-4F35-A432-01A25EAC8C59}"/>
+    <workbookView visibility="visible" minimized="1" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1932" yWindow="0" windowWidth="20928" windowHeight="12240" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Preset1" sheetId="1" r:id="rId1"/>
-    <sheet name="Preset2" sheetId="3" r:id="rId2"/>
+    <sheet name="Preset1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Preset2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Preset1.xml" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Preset2.xml" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{544D22BF-B1BE-40FF-A70C-19DD8D26861C}" name="fan" type="4" refreshedVersion="0" background="1">
-    <webPr xml="1" sourceData="1" url="C:\Users\morch\Downloads\fan.xml" htmlTables="1" htmlFormat="all"/>
-  </connection>
-</connections>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Pan</t>
-  </si>
-  <si>
-    <t>Tilt</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -90,96 +49,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/xmlMaps.xml><?xml version="1.0" encoding="utf-8"?>
-<MapInfo xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" SelectionNamespaces="">
-  <Schema ID="Schema1">
-    <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="">
-      <xsd:element nillable="true" name="GMA3">
-        <xsd:complexType>
-          <xsd:sequence minOccurs="0">
-            <xsd:element minOccurs="0" nillable="true" name="Preset" form="unqualified">
-              <xsd:complexType>
-                <xsd:sequence minOccurs="0">
-                  <xsd:element minOccurs="0" nillable="true" name="PresetData" form="unqualified">
-                    <xsd:complexType>
-                      <xsd:sequence minOccurs="0">
-                        <xsd:element minOccurs="0" maxOccurs="unbounded" nillable="true" name="Phaser" form="unqualified">
-                          <xsd:complexType>
-                            <xsd:sequence minOccurs="0">
-                              <xsd:element minOccurs="0" nillable="true" name="Step" form="unqualified">
-                                <xsd:complexType>
-                                  <xsd:attribute name="Function" form="unqualified" type="xsd:string"/>
-                                  <xsd:attribute name="AbsolutePhys" form="unqualified" type="xsd:double"/>
-                                </xsd:complexType>
-                              </xsd:element>
-                            </xsd:sequence>
-                            <xsd:attribute name="IDType" form="unqualified" type="xsd:integer"/>
-                            <xsd:attribute name="ID" form="unqualified" type="xsd:integer"/>
-                            <xsd:attribute name="Attribute" form="unqualified" type="xsd:string"/>
-                            <xsd:attribute name="GridPos" form="unqualified" type="xsd:integer"/>
-                            <xsd:attribute name="Selective" form="unqualified" type="xsd:boolean"/>
-                          </xsd:complexType>
-                        </xsd:element>
-                      </xsd:sequence>
-                      <xsd:attribute name="Size" form="unqualified" type="xsd:integer"/>
-                    </xsd:complexType>
-                  </xsd:element>
-                </xsd:sequence>
-                <xsd:attribute name="Name" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="Guid" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="Active" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="ShuffleMode" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="Xinv" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="XinvB" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="XinvG" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="XinvW" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="Yinv" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="YinvB" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="YinvG" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="YinvW" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="Zinv" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="ZinvB" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="ZinvG" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="ZinvW" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="InvertX" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="InvertY" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="InvertZ" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="MAgic" form="unqualified" type="xsd:string"/>
-                <xsd:attribute name="Mode" form="unqualified" type="xsd:integer"/>
-              </xsd:complexType>
-            </xsd:element>
-          </xsd:sequence>
-          <xsd:attribute name="DataVersion" form="unqualified" type="xsd:string"/>
-        </xsd:complexType>
-      </xsd:element>
-    </xsd:schema>
-  </Schema>
-  <Map ID="1" Name="GMA3_Mappage" RootElement="GMA3" SchemaID="Schema1" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true">
-    <DataBinding FileBinding="true" ConnectionID="1" DataBindingLoadMode="1"/>
-  </Map>
-</MapInfo>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -498,40 +442,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83485C35-CD91-472C-B206-EFD8C855C57D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Pan</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tilt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>101</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>-50</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>-30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" t="n">
         <v>102</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>-41</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>-22</v>
       </c>
     </row>
@@ -541,44 +495,252 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398A69DF-A0C4-4E87-89A2-929A8A084A4D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Pan</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tilt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>101</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>-85.34</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>-30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" t="n">
         <v>102</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>-41</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>-22</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Pan</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tilt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>-20.0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-30.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-41.0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-22.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>9.999999</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-30.597927</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>29.999998</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-30.597927</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Pan</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tilt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>-85.34</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-30.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-41.0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-22.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>9.999999</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-30.597927</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>29.999998</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-30.597927</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>